--- a/artfynd/A 25081-2026 artfynd.xlsx
+++ b/artfynd/A 25081-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128609848</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,54 +791,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128609074</v>
+        <v>134158835</v>
       </c>
       <c r="B3" t="n">
-        <v>58005</v>
+        <v>75354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>6427</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Glansfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Diarthonis spadicea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Leight.) Frisch &amp; al.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lerjevallen, Sk</t>
+          <t>Lerjevallen V, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457191</v>
+        <v>457169</v>
       </c>
       <c r="R3" t="n">
-        <v>6229605</v>
+        <v>6229492</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,12 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,50 +873,51 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Hans Ingvarsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Hans Ingvarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129250694</v>
+        <v>129250699</v>
       </c>
       <c r="B4" t="n">
-        <v>58017</v>
+        <v>57247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>100038</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -987,6 +982,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>från andra sidan alkärr</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129250699</v>
+        <v>129251068</v>
       </c>
       <c r="B5" t="n">
-        <v>57029</v>
+        <v>57258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100038</v>
+        <v>100065</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>från andra sidan alkärr</t>
+          <t>Långt i norr</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,32 +1134,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129251068</v>
+        <v>128609074</v>
       </c>
       <c r="B6" t="n">
-        <v>57040</v>
+        <v>58238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100065</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1167,34 +1167,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lerjevallen Norr, Sk</t>
+          <t>Lerjevallen, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457254</v>
+        <v>457191</v>
       </c>
       <c r="R6" t="n">
-        <v>6229706</v>
+        <v>6229605</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,17 +1208,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Långt i norr</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,12 +1228,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1258,7 +1243,7 @@
         <v>129250653</v>
       </c>
       <c r="B7" t="n">
-        <v>58017</v>
+        <v>58238</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129250759</v>
+        <v>129250694</v>
       </c>
       <c r="B8" t="n">
-        <v>58017</v>
+        <v>58238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1386,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1425,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457336</v>
+        <v>457254</v>
       </c>
       <c r="R8" t="n">
-        <v>6229513</v>
+        <v>6229706</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1455,12 +1440,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1472,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129251070</v>
+        <v>129250759</v>
       </c>
       <c r="B9" t="n">
-        <v>57893</v>
+        <v>58238</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,26 +1483,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103020</v>
+        <v>103012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1541,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457254</v>
+        <v>457336</v>
       </c>
       <c r="R9" t="n">
-        <v>6229706</v>
+        <v>6229513</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1571,12 +1556,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,6 +1585,440 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129251070</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lerjevallen Norr, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>457254</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6229706</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Oppmanna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129373234</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lerjevallen, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>457015</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6229553</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Oppmanna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134220507</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99853</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222306</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stjärnstarr</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carex echinata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lerjevallen V, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>457296</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6229606</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Oppmanna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134158786</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99840</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222308</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rankstarr</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carex elongata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lerjevallen V, Sk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>457296</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6229606</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Oppmanna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25081-2026 artfynd.xlsx
+++ b/artfynd/A 25081-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128609848</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134158835</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129250699</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129251068</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128609074</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1353,6 +1383,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129250653</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1469,6 +1504,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129250694</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1585,6 +1625,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129250759</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1701,6 +1746,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129251070</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1815,6 +1865,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129373234</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1917,6 +1972,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134220507</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2019,8 +2079,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134158786</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>